--- a/TIME TABLE SAMPLE DATA/SUBJECT NO.OF CLASSES/II (GENERAL) SUBJECT AND PERIODS MAPPING.xlsx
+++ b/TIME TABLE SAMPLE DATA/SUBJECT NO.OF CLASSES/II (GENERAL) SUBJECT AND PERIODS MAPPING.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ganig\Desktop\Time_Table_\TIME TABLE SAMPLE DATA\SUBJECT NO.OF CLASSES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5D0B76C-B6A6-4AB5-A14A-2B4446D42AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3DB369-0FE2-4D29-A49C-AAA3A4CDCE7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{787A35D5-B610-4D15-9785-E55DACB48048}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{787A35D5-B610-4D15-9785-E55DACB48048}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -454,14 +454,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34FCE23-0E63-48B3-B26B-34080BF31F72}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.109375" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="3" max="3" width="34.21875" customWidth="1"/>
+    <col min="1" max="1" width="19.08984375" customWidth="1"/>
+    <col min="2" max="2" width="19.6328125" customWidth="1"/>
+    <col min="3" max="3" width="34.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -472,7 +472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -483,7 +483,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -494,7 +494,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -505,7 +505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -516,7 +516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -538,7 +538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -549,7 +549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -560,7 +560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -568,10 +568,10 @@
         <v>3</v>
       </c>
       <c r="C10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -582,7 +582,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -593,7 +593,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -604,7 +604,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
